--- a/poker/resources/sample/SharePromote.xlsx
+++ b/poker/resources/sample/SharePromote.xlsx
@@ -133,7 +133,7 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{;}</t>
+    <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -157,109 +157,109 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_100000</t>
+    <t>1990000_1000000</t>
   </si>
   <si>
     <t>档位2</t>
   </si>
   <si>
-    <t>1990000_200000</t>
-  </si>
-  <si>
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_300000</t>
+    <t>1990000_5000000</t>
   </si>
   <si>
     <t>档位4</t>
   </si>
   <si>
-    <t>1990000_400000</t>
-  </si>
-  <si>
     <t>档位5</t>
   </si>
   <si>
-    <t>1990000_500000</t>
+    <t>1990000_15000000</t>
   </si>
   <si>
     <t>档位6</t>
   </si>
   <si>
-    <t>1990000_600000</t>
+    <t>1990000_45000000</t>
   </si>
   <si>
     <t>档位7</t>
   </si>
   <si>
-    <t>1990000_700000</t>
+    <t>1990000_55000000</t>
   </si>
   <si>
     <t>档位8</t>
   </si>
   <si>
-    <t>1990000_800000</t>
+    <t>1990000_145000000</t>
   </si>
   <si>
     <t>档位9</t>
   </si>
   <si>
-    <t>1990000_1000000</t>
+    <t>1990000_255000000</t>
   </si>
   <si>
     <t>档位10</t>
   </si>
   <si>
+    <t>1990000_745000000</t>
+  </si>
+  <si>
+    <t>排名1</t>
+  </si>
+  <si>
+    <t>1990000_10000000</t>
+  </si>
+  <si>
+    <t>排名2</t>
+  </si>
+  <si>
+    <t>1990000_9000000</t>
+  </si>
+  <si>
+    <t>排名3</t>
+  </si>
+  <si>
+    <t>1990000_8000000</t>
+  </si>
+  <si>
+    <t>排名4</t>
+  </si>
+  <si>
+    <t>1990000_7000000</t>
+  </si>
+  <si>
+    <t>排名5</t>
+  </si>
+  <si>
+    <t>1990000_6000000</t>
+  </si>
+  <si>
+    <t>排名6-10</t>
+  </si>
+  <si>
+    <t>6_10</t>
+  </si>
+  <si>
+    <t>排名11-50</t>
+  </si>
+  <si>
+    <t>11_50</t>
+  </si>
+  <si>
+    <t>1990000_4000000</t>
+  </si>
+  <si>
+    <t>排名51-100</t>
+  </si>
+  <si>
+    <t>51_100</t>
+  </si>
+  <si>
     <t>1990000_3000000</t>
-  </si>
-  <si>
-    <t>排名1</t>
-  </si>
-  <si>
-    <t>1990000_1000000;1980000_500</t>
-  </si>
-  <si>
-    <t>排名2</t>
-  </si>
-  <si>
-    <t>1990000_900000;1980000_400</t>
-  </si>
-  <si>
-    <t>排名3</t>
-  </si>
-  <si>
-    <t>1990000_800000;1980000_300</t>
-  </si>
-  <si>
-    <t>排名4</t>
-  </si>
-  <si>
-    <t>1990000_700000;1980000_200</t>
-  </si>
-  <si>
-    <t>排名5</t>
-  </si>
-  <si>
-    <t>1990000_600000;1980000_100</t>
-  </si>
-  <si>
-    <t>排名6-10</t>
-  </si>
-  <si>
-    <t>6_10</t>
-  </si>
-  <si>
-    <t>排名11-50</t>
-  </si>
-  <si>
-    <t>11_50</t>
-  </si>
-  <si>
-    <t>排名51-100</t>
-  </si>
-  <si>
-    <t>51_100</t>
   </si>
 </sst>
 </file>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H6" s="9">
         <v>200</v>
@@ -1448,14 +1448,14 @@
         <v>1</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" s="9">
         <v>30</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" s="9">
         <v>300</v>
@@ -1470,14 +1470,14 @@
         <v>1</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="10">
         <v>50</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H8" s="9">
         <v>400</v>
@@ -1493,14 +1493,14 @@
         <v>1</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E9" s="9">
         <v>100</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H9" s="9">
         <v>500</v>
@@ -1516,14 +1516,14 @@
         <v>1</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E10" s="10">
         <v>300</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H10" s="9">
         <v>600</v>
@@ -1539,14 +1539,14 @@
         <v>1</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" s="9">
         <v>500</v>
       </c>
       <c r="F11" s="10"/>
       <c r="G11" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H11" s="9">
         <v>700</v>
@@ -1562,14 +1562,14 @@
         <v>1</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E12" s="10">
         <v>1000</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H12" s="9">
         <v>800</v>
@@ -1585,14 +1585,14 @@
         <v>1</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E13" s="9">
         <v>2000</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H13" s="9">
         <v>900</v>
@@ -1608,14 +1608,14 @@
         <v>1</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E14" s="9">
         <v>5000</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H14" s="9">
         <v>1000</v>
@@ -1631,14 +1631,14 @@
         <v>2</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="13">
         <v>1</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H15" s="12"/>
       <c r="K15" s="15"/>
@@ -1652,14 +1652,14 @@
         <v>2</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="13">
         <v>2</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H16" s="12"/>
       <c r="K16" s="15"/>
@@ -1673,14 +1673,14 @@
         <v>2</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="13">
         <v>3</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H17" s="12"/>
       <c r="K17" s="15"/>
@@ -1694,14 +1694,14 @@
         <v>2</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="13">
         <v>4</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H18" s="12"/>
       <c r="K18"/>
@@ -1715,14 +1715,14 @@
         <v>2</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="13">
         <v>5</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H19" s="12"/>
       <c r="K19"/>
@@ -1736,14 +1736,14 @@
         <v>2</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H20" s="12"/>
       <c r="K20"/>
@@ -1757,14 +1757,14 @@
         <v>2</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H21" s="12"/>
       <c r="K21"/>
@@ -1778,14 +1778,14 @@
         <v>2</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>21</v>
       </c>
       <c r="H22" s="12"/>
       <c r="K22"/>

--- a/poker/resources/sample/SharePromote.xlsx
+++ b/poker/resources/sample/SharePromote.xlsx
@@ -157,7 +157,7 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_1000000</t>
+    <t>1990000_1245000</t>
   </si>
   <si>
     <t>档位2</t>
@@ -166,7 +166,7 @@
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_5000000</t>
+    <t>1990000_4980000</t>
   </si>
   <si>
     <t>档位4</t>
@@ -175,67 +175,64 @@
     <t>档位5</t>
   </si>
   <si>
-    <t>1990000_15000000</t>
+    <t>1990000_12450000</t>
   </si>
   <si>
     <t>档位6</t>
   </si>
   <si>
-    <t>1990000_45000000</t>
+    <t>1990000_49800000</t>
   </si>
   <si>
     <t>档位7</t>
   </si>
   <si>
-    <t>1990000_55000000</t>
-  </si>
-  <si>
     <t>档位8</t>
   </si>
   <si>
-    <t>1990000_145000000</t>
+    <t>1990000_124500000</t>
   </si>
   <si>
     <t>档位9</t>
   </si>
   <si>
-    <t>1990000_255000000</t>
+    <t>1990000_249000000</t>
   </si>
   <si>
     <t>档位10</t>
   </si>
   <si>
-    <t>1990000_745000000</t>
+    <t>1990000_747000000</t>
   </si>
   <si>
     <t>排名1</t>
   </si>
   <si>
-    <t>1990000_10000000</t>
+    <t>1990000_16000000</t>
   </si>
   <si>
     <t>排名2</t>
   </si>
   <si>
-    <t>1990000_9000000</t>
+    <t>1990000_12000000</t>
   </si>
   <si>
     <t>排名3</t>
   </si>
   <si>
-    <t>1990000_8000000</t>
+    <t>1990000_9500000</t>
   </si>
   <si>
     <t>排名4</t>
   </si>
   <si>
-    <t>1990000_7000000</t>
+    <t>1990000_6500000</t>
   </si>
   <si>
     <t>排名5</t>
   </si>
   <si>
-    <t>1990000_6000000</t>
+    <t>1990000_4000000</t>
   </si>
   <si>
     <t>排名6-10</t>
@@ -244,13 +241,16 @@
     <t>6_10</t>
   </si>
   <si>
+    <t>1990000_2500000</t>
+  </si>
+  <si>
     <t>排名11-50</t>
   </si>
   <si>
     <t>11_50</t>
   </si>
   <si>
-    <t>1990000_4000000</t>
+    <t>1990000_600000</t>
   </si>
   <si>
     <t>排名51-100</t>
@@ -259,7 +259,7 @@
     <t>51_100</t>
   </si>
   <si>
-    <t>1990000_3000000</t>
+    <t>1990000_300000</t>
   </si>
 </sst>
 </file>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="F11" s="10"/>
       <c r="G11" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H11" s="9">
         <v>700</v>
@@ -1562,14 +1562,14 @@
         <v>1</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12" s="10">
         <v>1000</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H12" s="9">
         <v>800</v>
@@ -1585,14 +1585,14 @@
         <v>1</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" s="9">
         <v>2000</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H13" s="9">
         <v>900</v>
@@ -1608,14 +1608,14 @@
         <v>1</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" s="9">
         <v>5000</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H14" s="9">
         <v>1000</v>
@@ -1631,14 +1631,14 @@
         <v>2</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="13">
         <v>1</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H15" s="12"/>
       <c r="K15" s="15"/>
@@ -1652,14 +1652,14 @@
         <v>2</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="13">
         <v>2</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H16" s="12"/>
       <c r="K16" s="15"/>
@@ -1673,14 +1673,14 @@
         <v>2</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="13">
         <v>3</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H17" s="12"/>
       <c r="K17" s="15"/>
@@ -1694,14 +1694,14 @@
         <v>2</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="13">
         <v>4</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H18" s="12"/>
       <c r="K18"/>
@@ -1715,14 +1715,14 @@
         <v>2</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="13">
         <v>5</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H19" s="12"/>
       <c r="K19"/>
@@ -1736,14 +1736,14 @@
         <v>2</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="14" t="s">
         <v>45</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>20</v>
       </c>
       <c r="H20" s="12"/>
       <c r="K20"/>

--- a/poker/resources/sample/SharePromote.xlsx
+++ b/poker/resources/sample/SharePromote.xlsx
@@ -157,7 +157,7 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_1245000</t>
+    <t>1990000_8715000</t>
   </si>
   <si>
     <t>档位2</t>
@@ -166,7 +166,7 @@
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_4980000</t>
+    <t>1990000_34860000</t>
   </si>
   <si>
     <t>档位4</t>
@@ -175,13 +175,13 @@
     <t>档位5</t>
   </si>
   <si>
-    <t>1990000_12450000</t>
+    <t>1990000_87150000</t>
   </si>
   <si>
     <t>档位6</t>
   </si>
   <si>
-    <t>1990000_49800000</t>
+    <t>1990000_348600000</t>
   </si>
   <si>
     <t>档位7</t>
@@ -190,49 +190,49 @@
     <t>档位8</t>
   </si>
   <si>
-    <t>1990000_124500000</t>
+    <t>1990000_871500000</t>
   </si>
   <si>
     <t>档位9</t>
   </si>
   <si>
-    <t>1990000_249000000</t>
+    <t>1990000_1743000000</t>
   </si>
   <si>
     <t>档位10</t>
   </si>
   <si>
-    <t>1990000_747000000</t>
+    <t>1990000_5229000000</t>
   </si>
   <si>
     <t>排名1</t>
   </si>
   <si>
-    <t>1990000_16000000</t>
+    <t>1990000_112000000</t>
   </si>
   <si>
     <t>排名2</t>
   </si>
   <si>
-    <t>1990000_12000000</t>
+    <t>1990000_84000000</t>
   </si>
   <si>
     <t>排名3</t>
   </si>
   <si>
-    <t>1990000_9500000</t>
+    <t>1990000_66500000</t>
   </si>
   <si>
     <t>排名4</t>
   </si>
   <si>
-    <t>1990000_6500000</t>
+    <t>1990000_45500000</t>
   </si>
   <si>
     <t>排名5</t>
   </si>
   <si>
-    <t>1990000_4000000</t>
+    <t>1990000_28000000</t>
   </si>
   <si>
     <t>排名6-10</t>
@@ -241,7 +241,7 @@
     <t>6_10</t>
   </si>
   <si>
-    <t>1990000_2500000</t>
+    <t>1990000_17500000</t>
   </si>
   <si>
     <t>排名11-50</t>
@@ -250,7 +250,7 @@
     <t>11_50</t>
   </si>
   <si>
-    <t>1990000_600000</t>
+    <t>1990000_4200000</t>
   </si>
   <si>
     <t>排名51-100</t>
@@ -259,7 +259,7 @@
     <t>51_100</t>
   </si>
   <si>
-    <t>1990000_300000</t>
+    <t>1990000_2100000</t>
   </si>
 </sst>
 </file>
@@ -442,12 +442,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -949,6 +949,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -959,9 +962,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1317,7 +1317,7 @@
     <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:11">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:11">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:11">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:11">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -1395,7 +1395,7 @@
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:8">
+    <row r="5" s="1" customFormat="1" spans="1:11">
       <c r="A5" s="9">
         <v>1</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
+    <row r="6" s="1" customFormat="1" spans="1:11">
       <c r="A6" s="9">
         <v>2</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:8">
+    <row r="7" s="1" customFormat="1" spans="1:11">
       <c r="A7" s="9">
         <v>3</v>
       </c>
@@ -1482,7 +1482,7 @@
       <c r="H8" s="9">
         <v>400</v>
       </c>
-      <c r="K8" s="15"/>
+      <c r="K8" s="11"/>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:11">
       <c r="A9" s="10">
@@ -1505,7 +1505,7 @@
       <c r="H9" s="9">
         <v>500</v>
       </c>
-      <c r="K9" s="15"/>
+      <c r="K9" s="11"/>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:11">
       <c r="A10" s="10">
@@ -1528,7 +1528,7 @@
       <c r="H10" s="9">
         <v>600</v>
       </c>
-      <c r="K10" s="15"/>
+      <c r="K10" s="11"/>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:11">
       <c r="A11" s="10">
@@ -1551,7 +1551,7 @@
       <c r="H11" s="9">
         <v>700</v>
       </c>
-      <c r="K11" s="15"/>
+      <c r="K11" s="11"/>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:11">
       <c r="A12" s="10">
@@ -1574,7 +1574,7 @@
       <c r="H12" s="9">
         <v>800</v>
       </c>
-      <c r="K12" s="15"/>
+      <c r="K12" s="11"/>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:11">
       <c r="A13" s="10">
@@ -1590,14 +1590,14 @@
       <c r="E13" s="9">
         <v>2000</v>
       </c>
-      <c r="F13" s="11"/>
+      <c r="F13" s="12"/>
       <c r="G13" s="9" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="9">
         <v>900</v>
       </c>
-      <c r="K13" s="15"/>
+      <c r="K13" s="11"/>
     </row>
     <row r="14" s="2" customFormat="1" spans="1:11">
       <c r="A14" s="10">
@@ -1613,193 +1613,193 @@
       <c r="E14" s="9">
         <v>5000</v>
       </c>
-      <c r="F14" s="11"/>
+      <c r="F14" s="12"/>
       <c r="G14" s="9" t="s">
         <v>32</v>
       </c>
       <c r="H14" s="9">
         <v>1000</v>
       </c>
-      <c r="K14" s="15"/>
+      <c r="K14" s="11"/>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:11">
-      <c r="A15" s="12">
+      <c r="A15" s="13">
         <v>101</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12">
+      <c r="B15" s="13"/>
+      <c r="C15" s="13">
         <v>2</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="13">
+      <c r="E15" s="13"/>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="12"/>
-      <c r="K15" s="15"/>
+      <c r="H15" s="13"/>
+      <c r="K15" s="11"/>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:11">
-      <c r="A16" s="12">
+      <c r="A16" s="13">
         <v>102</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12">
+      <c r="B16" s="13"/>
+      <c r="C16" s="13">
         <v>2</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="13">
+      <c r="E16" s="13"/>
+      <c r="F16" s="14">
         <v>2</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="12"/>
-      <c r="K16" s="15"/>
+      <c r="H16" s="13"/>
+      <c r="K16" s="11"/>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:11">
-      <c r="A17" s="12">
+      <c r="A17" s="13">
         <v>103</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12">
+      <c r="B17" s="13"/>
+      <c r="C17" s="13">
         <v>2</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="13">
+      <c r="E17" s="13"/>
+      <c r="F17" s="14">
         <v>3</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="H17" s="12"/>
-      <c r="K17" s="15"/>
+      <c r="H17" s="13"/>
+      <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="12">
+      <c r="A18" s="13">
         <v>104</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12">
+      <c r="B18" s="13"/>
+      <c r="C18" s="13">
         <v>2</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="13">
+      <c r="E18" s="13"/>
+      <c r="F18" s="14">
         <v>4</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="12"/>
+      <c r="H18" s="13"/>
       <c r="K18"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="12">
+      <c r="A19" s="13">
         <v>105</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12">
+      <c r="B19" s="13"/>
+      <c r="C19" s="13">
         <v>2</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="13">
+      <c r="E19" s="13"/>
+      <c r="F19" s="14">
         <v>5</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="H19" s="12"/>
+      <c r="H19" s="13"/>
       <c r="K19"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="12">
+      <c r="A20" s="13">
         <v>106</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13">
         <v>2</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="13" t="s">
+      <c r="E20" s="13"/>
+      <c r="F20" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="H20" s="12"/>
+      <c r="H20" s="13"/>
       <c r="K20"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="12">
+      <c r="A21" s="13">
         <v>107</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12">
+      <c r="B21" s="13"/>
+      <c r="C21" s="13">
         <v>2</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="13" t="s">
+      <c r="E21" s="13"/>
+      <c r="F21" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="12"/>
+      <c r="H21" s="13"/>
       <c r="K21"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="12">
+      <c r="A22" s="13">
         <v>108</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12">
+      <c r="B22" s="13"/>
+      <c r="C22" s="13">
         <v>2</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="13" t="s">
+      <c r="E22" s="13"/>
+      <c r="F22" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="H22" s="12"/>
+      <c r="H22" s="13"/>
       <c r="K22"/>
     </row>
-    <row r="23" spans="11:11">
+    <row r="23" spans="1:11">
       <c r="K23"/>
     </row>
-    <row r="24" spans="11:11">
+    <row r="24" spans="1:11">
       <c r="K24"/>
     </row>
-    <row r="25" spans="11:11">
+    <row r="25" spans="1:11">
       <c r="K25"/>
     </row>
-    <row r="26" spans="11:11">
+    <row r="26" spans="1:11">
       <c r="K26"/>
     </row>
   </sheetData>

--- a/poker/resources/sample/SharePromote.xlsx
+++ b/poker/resources/sample/SharePromote.xlsx
@@ -442,12 +442,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1407,7 +1407,7 @@
         <v>16</v>
       </c>
       <c r="E5" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="9" t="s">

--- a/poker/resources/sample/SharePromote.xlsx
+++ b/poker/resources/sample/SharePromote.xlsx
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="134">
   <si>
     <t>序列ID</t>
   </si>
@@ -157,82 +157,328 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_8715000</t>
+    <t>1990000_5512000</t>
   </si>
   <si>
     <t>档位2</t>
   </si>
   <si>
+    <t>1990000_5880000</t>
+  </si>
+  <si>
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_34860000</t>
+    <t>1990000_6247000</t>
   </si>
   <si>
     <t>档位4</t>
   </si>
   <si>
+    <t>1990000_6615000</t>
+  </si>
+  <si>
     <t>档位5</t>
   </si>
   <si>
-    <t>1990000_87150000</t>
+    <t>1990000_6982000</t>
   </si>
   <si>
     <t>档位6</t>
   </si>
   <si>
-    <t>1990000_348600000</t>
+    <t>1990000_7533000</t>
   </si>
   <si>
     <t>档位7</t>
   </si>
   <si>
+    <t>1990000_8085000</t>
+  </si>
+  <si>
     <t>档位8</t>
   </si>
   <si>
-    <t>1990000_871500000</t>
+    <t>1990000_8452000</t>
   </si>
   <si>
     <t>档位9</t>
   </si>
   <si>
-    <t>1990000_1743000000</t>
+    <t>1990000_8820000</t>
   </si>
   <si>
     <t>档位10</t>
   </si>
   <si>
-    <t>1990000_5229000000</t>
+    <t>1990000_9187000</t>
+  </si>
+  <si>
+    <t>档位11</t>
+  </si>
+  <si>
+    <t>1990000_10237000</t>
+  </si>
+  <si>
+    <t>档位12</t>
+  </si>
+  <si>
+    <t>1990000_10920000</t>
+  </si>
+  <si>
+    <t>档位13</t>
+  </si>
+  <si>
+    <t>1990000_11602000</t>
+  </si>
+  <si>
+    <t>档位14</t>
+  </si>
+  <si>
+    <t>1990000_12285000</t>
+  </si>
+  <si>
+    <t>档位15</t>
+  </si>
+  <si>
+    <t>1990000_12967000</t>
+  </si>
+  <si>
+    <t>档位16</t>
+  </si>
+  <si>
+    <t>1990000_13991000</t>
+  </si>
+  <si>
+    <t>档位17</t>
+  </si>
+  <si>
+    <t>1990000_15015000</t>
+  </si>
+  <si>
+    <t>档位18</t>
+  </si>
+  <si>
+    <t>1990000_15697000</t>
+  </si>
+  <si>
+    <t>档位19</t>
+  </si>
+  <si>
+    <t>1990000_16380000</t>
+  </si>
+  <si>
+    <t>档位20</t>
+  </si>
+  <si>
+    <t>1990000_17062000</t>
+  </si>
+  <si>
+    <t>档位21</t>
+  </si>
+  <si>
+    <t>1990000_21000000</t>
+  </si>
+  <si>
+    <t>档位22</t>
+  </si>
+  <si>
+    <t>1990000_22400000</t>
+  </si>
+  <si>
+    <t>档位23</t>
+  </si>
+  <si>
+    <t>1990000_23800000</t>
+  </si>
+  <si>
+    <t>档位24</t>
+  </si>
+  <si>
+    <t>1990000_25200000</t>
+  </si>
+  <si>
+    <t>档位25</t>
+  </si>
+  <si>
+    <t>1990000_26600000</t>
+  </si>
+  <si>
+    <t>档位26</t>
+  </si>
+  <si>
+    <t>1990000_28700000</t>
+  </si>
+  <si>
+    <t>档位27</t>
+  </si>
+  <si>
+    <t>1990000_30800000</t>
+  </si>
+  <si>
+    <t>档位28</t>
+  </si>
+  <si>
+    <t>1990000_32200000</t>
+  </si>
+  <si>
+    <t>档位29</t>
+  </si>
+  <si>
+    <t>1990000_33600000</t>
+  </si>
+  <si>
+    <t>档位30</t>
+  </si>
+  <si>
+    <t>1990000_35000000</t>
+  </si>
+  <si>
+    <t>档位31</t>
+  </si>
+  <si>
+    <t>1990000_42000000</t>
+  </si>
+  <si>
+    <t>档位32</t>
+  </si>
+  <si>
+    <t>1990000_44800000</t>
+  </si>
+  <si>
+    <t>档位33</t>
+  </si>
+  <si>
+    <t>1990000_47600000</t>
+  </si>
+  <si>
+    <t>档位34</t>
+  </si>
+  <si>
+    <t>1990000_50400000</t>
+  </si>
+  <si>
+    <t>档位35</t>
+  </si>
+  <si>
+    <t>1990000_53200000</t>
+  </si>
+  <si>
+    <t>档位36</t>
+  </si>
+  <si>
+    <t>1990000_57400000</t>
+  </si>
+  <si>
+    <t>档位37</t>
+  </si>
+  <si>
+    <t>1990000_61600000</t>
+  </si>
+  <si>
+    <t>档位38</t>
+  </si>
+  <si>
+    <t>1990000_64400000</t>
+  </si>
+  <si>
+    <t>档位39</t>
+  </si>
+  <si>
+    <t>1990000_67200000</t>
+  </si>
+  <si>
+    <t>档位40</t>
+  </si>
+  <si>
+    <t>1990000_70000000</t>
+  </si>
+  <si>
+    <t>档位41</t>
+  </si>
+  <si>
+    <t>1990000_89250000</t>
+  </si>
+  <si>
+    <t>档位42</t>
+  </si>
+  <si>
+    <t>1990000_95200000</t>
+  </si>
+  <si>
+    <t>档位43</t>
+  </si>
+  <si>
+    <t>1990000_101150000</t>
+  </si>
+  <si>
+    <t>档位44</t>
+  </si>
+  <si>
+    <t>1990000_107100000</t>
+  </si>
+  <si>
+    <t>档位45</t>
+  </si>
+  <si>
+    <t>1990000_113050000</t>
+  </si>
+  <si>
+    <t>档位46</t>
+  </si>
+  <si>
+    <t>1990000_121975000</t>
+  </si>
+  <si>
+    <t>档位47</t>
+  </si>
+  <si>
+    <t>1990000_130900000</t>
+  </si>
+  <si>
+    <t>档位48</t>
+  </si>
+  <si>
+    <t>1990000_136850000</t>
+  </si>
+  <si>
+    <t>档位49</t>
+  </si>
+  <si>
+    <t>1990000_142800000</t>
+  </si>
+  <si>
+    <t>档位50</t>
+  </si>
+  <si>
+    <t>1990000_148750000</t>
   </si>
   <si>
     <t>排名1</t>
   </si>
   <si>
-    <t>1990000_112000000</t>
+    <t>1990000_56000000</t>
   </si>
   <si>
     <t>排名2</t>
   </si>
   <si>
-    <t>1990000_84000000</t>
-  </si>
-  <si>
     <t>排名3</t>
   </si>
   <si>
-    <t>1990000_66500000</t>
+    <t>1990000_33250000</t>
   </si>
   <si>
     <t>排名4</t>
   </si>
   <si>
-    <t>1990000_45500000</t>
+    <t>1990000_22750000</t>
   </si>
   <si>
     <t>排名5</t>
   </si>
   <si>
-    <t>1990000_28000000</t>
+    <t>1990000_14000000</t>
   </si>
   <si>
     <t>排名6-10</t>
@@ -241,7 +487,7 @@
     <t>6_10</t>
   </si>
   <si>
-    <t>1990000_17500000</t>
+    <t>1990000_8750000</t>
   </si>
   <si>
     <t>排名11-50</t>
@@ -250,7 +496,7 @@
     <t>11_50</t>
   </si>
   <si>
-    <t>1990000_4200000</t>
+    <t>1990000_2100000</t>
   </si>
   <si>
     <t>排名51-100</t>
@@ -259,7 +505,7 @@
     <t>51_100</t>
   </si>
   <si>
-    <t>1990000_2100000</t>
+    <t>1990000_1050000</t>
   </si>
 </sst>
 </file>
@@ -453,7 +699,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -468,13 +714,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -791,7 +1043,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -815,16 +1067,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -833,89 +1085,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -958,10 +1210,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1303,7 +1558,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="7" style="3" customWidth="1"/>
@@ -1414,7 +1669,7 @@
         <v>17</v>
       </c>
       <c r="H5" s="9">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:11">
@@ -1429,14 +1684,14 @@
         <v>18</v>
       </c>
       <c r="E6" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H6" s="9">
-        <v>200</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:11">
@@ -1448,17 +1703,17 @@
         <v>1</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" s="9">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="9">
-        <v>300</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:11">
@@ -1470,17 +1725,17 @@
         <v>1</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="10">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H8" s="9">
-        <v>400</v>
+        <v>80</v>
       </c>
       <c r="K8" s="11"/>
     </row>
@@ -1493,17 +1748,17 @@
         <v>1</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E9" s="9">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H9" s="9">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="K9" s="11"/>
     </row>
@@ -1516,17 +1771,17 @@
         <v>1</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E10" s="10">
-        <v>300</v>
+        <v>58</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H10" s="9">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="K10" s="11"/>
     </row>
@@ -1539,17 +1794,17 @@
         <v>1</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E11" s="9">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="F11" s="10"/>
       <c r="G11" s="9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H11" s="9">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="K11" s="11"/>
     </row>
@@ -1562,17 +1817,17 @@
         <v>1</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E12" s="10">
-        <v>1000</v>
+        <v>82</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H12" s="9">
-        <v>800</v>
+        <v>160</v>
       </c>
       <c r="K12" s="11"/>
     </row>
@@ -1585,17 +1840,17 @@
         <v>1</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E13" s="9">
-        <v>2000</v>
+        <v>94</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H13" s="9">
-        <v>900</v>
+        <v>180</v>
       </c>
       <c r="K13" s="11"/>
     </row>
@@ -1608,199 +1863,1071 @@
         <v>1</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E14" s="9">
-        <v>5000</v>
+        <v>105</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="9">
+        <v>200</v>
+      </c>
+      <c r="K14" s="11"/>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:11">
+      <c r="A15" s="10">
+        <v>11</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10">
+        <v>1</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="10">
+        <v>120</v>
+      </c>
+      <c r="F15" s="12"/>
+      <c r="G15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="10">
+        <v>220</v>
+      </c>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:11">
+      <c r="A16" s="10">
+        <v>12</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10">
+        <v>1</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="10">
+        <v>140</v>
+      </c>
+      <c r="F16" s="12"/>
+      <c r="G16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="10">
+        <v>240</v>
+      </c>
+      <c r="K16" s="11"/>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:11">
+      <c r="A17" s="10">
+        <v>13</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10">
+        <v>1</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="10">
+        <v>160</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" s="10">
+        <v>260</v>
+      </c>
+      <c r="K17" s="11"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="10">
+        <v>14</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10">
+        <v>1</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="10">
+        <v>180</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="10">
+        <v>280</v>
+      </c>
+      <c r="K18"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="10">
+        <v>15</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10">
+        <v>1</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="10">
+        <v>200</v>
+      </c>
+      <c r="F19" s="12"/>
+      <c r="G19" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="10">
+        <v>300</v>
+      </c>
+      <c r="K19"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="10">
+        <v>16</v>
+      </c>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10">
+        <v>1</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="10">
+        <v>220</v>
+      </c>
+      <c r="F20" s="12"/>
+      <c r="G20" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="10">
+        <v>320</v>
+      </c>
+      <c r="K20"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="10">
+        <v>17</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10">
+        <v>1</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="10">
+        <v>240</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21" s="10">
+        <v>340</v>
+      </c>
+      <c r="K21"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="10">
+        <v>18</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10">
+        <v>1</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="10">
+        <v>260</v>
+      </c>
+      <c r="F22" s="12"/>
+      <c r="G22" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H22" s="10">
+        <v>360</v>
+      </c>
+      <c r="K22"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="13">
+        <v>19</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13">
+        <v>1</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="13">
+        <v>280</v>
+      </c>
+      <c r="F23" s="14"/>
+      <c r="G23" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H23" s="13">
+        <v>380</v>
+      </c>
+      <c r="K23"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="13">
+        <v>20</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13">
+        <v>1</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E24" s="13">
+        <v>300</v>
+      </c>
+      <c r="F24" s="14"/>
+      <c r="G24" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H24" s="13">
+        <v>400</v>
+      </c>
+      <c r="K24"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="13">
+        <v>21</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13">
+        <v>1</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="13">
+        <v>340</v>
+      </c>
+      <c r="F25" s="14"/>
+      <c r="G25" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H25" s="13">
+        <v>420</v>
+      </c>
+      <c r="K25"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="13">
+        <v>22</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13">
+        <v>1</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="13">
+        <v>380</v>
+      </c>
+      <c r="F26" s="14"/>
+      <c r="G26" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H26" s="13">
+        <v>440</v>
+      </c>
+      <c r="K26"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="13">
+        <v>23</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="13">
+        <v>420</v>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="G27" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="H27" s="13">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="13">
+        <v>24</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="13">
+        <v>460</v>
+      </c>
+      <c r="F28" s="14"/>
+      <c r="G28" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H28" s="13">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="13">
+        <v>25</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="13">
+        <v>500</v>
+      </c>
+      <c r="F29" s="14"/>
+      <c r="G29" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H29" s="13">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="13">
+        <v>26</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13">
+        <v>1</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" s="13">
+        <v>540</v>
+      </c>
+      <c r="F30" s="14"/>
+      <c r="G30" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H30" s="13">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="13">
+        <v>27</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" s="13">
+        <v>580</v>
+      </c>
+      <c r="F31" s="14"/>
+      <c r="G31" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H31" s="13">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="13">
+        <v>28</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13">
+        <v>1</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E32" s="13">
+        <v>620</v>
+      </c>
+      <c r="F32" s="14"/>
+      <c r="G32" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H32" s="13">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="13">
+        <v>29</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33" s="13">
+        <v>660</v>
+      </c>
+      <c r="F33" s="14"/>
+      <c r="G33" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H33" s="13">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="13">
+        <v>30</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13">
+        <v>1</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="13">
+        <v>700</v>
+      </c>
+      <c r="F34" s="14"/>
+      <c r="G34" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H34" s="13">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="13">
+        <v>31</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13">
+        <v>1</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E35" s="13">
+        <v>780</v>
+      </c>
+      <c r="F35" s="14"/>
+      <c r="G35" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="H35" s="13">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="13">
         <v>32</v>
       </c>
-      <c r="H14" s="9">
+      <c r="B36" s="13"/>
+      <c r="C36" s="13">
+        <v>1</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E36" s="13">
+        <v>860</v>
+      </c>
+      <c r="F36" s="14"/>
+      <c r="G36" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H36" s="13">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="13">
+        <v>33</v>
+      </c>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13">
+        <v>1</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E37" s="13">
+        <v>940</v>
+      </c>
+      <c r="F37" s="14"/>
+      <c r="G37" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H37" s="13">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="13">
+        <v>34</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13">
+        <v>1</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E38" s="13">
+        <v>1020</v>
+      </c>
+      <c r="F38" s="14"/>
+      <c r="G38" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H38" s="13">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="13">
+        <v>35</v>
+      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13">
+        <v>1</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E39" s="13">
+        <v>1100</v>
+      </c>
+      <c r="F39" s="14"/>
+      <c r="G39" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="H39" s="13">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="13">
+        <v>36</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13">
+        <v>1</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E40" s="13">
+        <v>1180</v>
+      </c>
+      <c r="F40" s="14"/>
+      <c r="G40" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H40" s="13">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="13">
+        <v>37</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13">
+        <v>1</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E41" s="13">
+        <v>1260</v>
+      </c>
+      <c r="F41" s="14"/>
+      <c r="G41" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="H41" s="13">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="13">
+        <v>38</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13">
+        <v>1</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" s="13">
+        <v>1340</v>
+      </c>
+      <c r="F42" s="14"/>
+      <c r="G42" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="H42" s="13">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="13">
+        <v>39</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13">
+        <v>1</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E43" s="13">
+        <v>1420</v>
+      </c>
+      <c r="F43" s="14"/>
+      <c r="G43" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H43" s="13">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="13">
+        <v>40</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13">
+        <v>1</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="13">
+        <v>1500</v>
+      </c>
+      <c r="F44" s="14"/>
+      <c r="G44" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H44" s="13">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="13">
+        <v>41</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13">
+        <v>1</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E45" s="13">
+        <v>1670</v>
+      </c>
+      <c r="F45" s="14"/>
+      <c r="G45" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="H45" s="13">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="13">
+        <v>42</v>
+      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13">
+        <v>1</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E46" s="13">
+        <v>1840</v>
+      </c>
+      <c r="F46" s="14"/>
+      <c r="G46" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="H46" s="13">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="13">
+        <v>43</v>
+      </c>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13">
+        <v>1</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E47" s="13">
+        <v>2010</v>
+      </c>
+      <c r="F47" s="14"/>
+      <c r="G47" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="H47" s="13">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="13">
+        <v>44</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13">
+        <v>1</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E48" s="13">
+        <v>2180</v>
+      </c>
+      <c r="F48" s="14"/>
+      <c r="G48" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="H48" s="13">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="13">
+        <v>45</v>
+      </c>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13">
+        <v>1</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E49" s="13">
+        <v>2350</v>
+      </c>
+      <c r="F49" s="14"/>
+      <c r="G49" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H49" s="13">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="13">
+        <v>46</v>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13">
+        <v>1</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E50" s="13">
+        <v>2520</v>
+      </c>
+      <c r="F50" s="14"/>
+      <c r="G50" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H50" s="13">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="13">
+        <v>47</v>
+      </c>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13">
+        <v>1</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" s="13">
+        <v>2690</v>
+      </c>
+      <c r="F51" s="14"/>
+      <c r="G51" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H51" s="13">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="13">
+        <v>48</v>
+      </c>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13">
+        <v>1</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E52" s="13">
+        <v>2860</v>
+      </c>
+      <c r="F52" s="14"/>
+      <c r="G52" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="H52" s="13">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="13">
+        <v>49</v>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13">
+        <v>1</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E53" s="13">
+        <v>3030</v>
+      </c>
+      <c r="F53" s="14"/>
+      <c r="G53" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="H53" s="13">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="13">
+        <v>50</v>
+      </c>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13">
+        <v>1</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E54" s="13">
+        <v>3200</v>
+      </c>
+      <c r="F54" s="14"/>
+      <c r="G54" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="H54" s="13">
         <v>1000</v>
       </c>
-      <c r="K14" s="11"/>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:11">
-      <c r="A15" s="13">
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="15">
         <v>101</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13">
+      <c r="B55" s="15"/>
+      <c r="C55" s="15">
         <v>2</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="13"/>
-      <c r="K15" s="11"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:11">
-      <c r="A16" s="13">
+      <c r="D55" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E55" s="15"/>
+      <c r="F55" s="16">
+        <v>1</v>
+      </c>
+      <c r="G55" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="H55" s="15"/>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="15">
         <v>102</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13">
+      <c r="B56" s="15"/>
+      <c r="C56" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="14">
+      <c r="D56" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E56" s="15"/>
+      <c r="F56" s="16">
         <v>2</v>
       </c>
-      <c r="G16" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="13"/>
-      <c r="K16" s="11"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:11">
-      <c r="A17" s="13">
+      <c r="G56" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H56" s="15"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="15">
         <v>103</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13">
+      <c r="B57" s="15"/>
+      <c r="C57" s="15">
         <v>2</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="14">
+      <c r="D57" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E57" s="15"/>
+      <c r="F57" s="16">
         <v>3</v>
       </c>
-      <c r="G17" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="H17" s="13"/>
-      <c r="K17" s="11"/>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="13">
+      <c r="G57" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="H57" s="15"/>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="15">
         <v>104</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13">
+      <c r="B58" s="15"/>
+      <c r="C58" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="14">
+      <c r="D58" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="E58" s="15"/>
+      <c r="F58" s="16">
         <v>4</v>
       </c>
-      <c r="G18" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18" s="13"/>
-      <c r="K18"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="13">
+      <c r="G58" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="H58" s="15"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="15">
         <v>105</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13">
+      <c r="B59" s="15"/>
+      <c r="C59" s="15">
         <v>2</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="14">
+      <c r="D59" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E59" s="15"/>
+      <c r="F59" s="16">
         <v>5</v>
       </c>
-      <c r="G19" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="H19" s="13"/>
-      <c r="K19"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="13">
+      <c r="G59" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H59" s="15"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="15">
         <v>106</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13">
+      <c r="B60" s="15"/>
+      <c r="C60" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="H20" s="13"/>
-      <c r="K20"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="13">
+      <c r="D60" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E60" s="15"/>
+      <c r="F60" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="G60" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="H60" s="15"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="15">
         <v>107</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13">
+      <c r="B61" s="15"/>
+      <c r="C61" s="15">
         <v>2</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E21" s="13"/>
-      <c r="F21" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="H21" s="13"/>
-      <c r="K21"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="13">
+      <c r="D61" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E61" s="15"/>
+      <c r="F61" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="G61" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="H61" s="15"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="15">
         <v>108</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13">
+      <c r="B62" s="15"/>
+      <c r="C62" s="15">
         <v>2</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="H22" s="13"/>
-      <c r="K22"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="K23"/>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="K24"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="K25"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="K26"/>
+      <c r="D62" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E62" s="15"/>
+      <c r="F62" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G62" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="H62" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/poker/resources/sample/SharePromote.xlsx
+++ b/poker/resources/sample/SharePromote.xlsx
@@ -95,7 +95,33 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-累积收益比例</t>
+有效下级用户每笔充值获得此值的万分比提成奖励
+实际获得返利金额  =  充值货币 × 【充值对应金币】 × 此值 ÷10000
+充值对应金币在globalConfig表中 ID  53 推广分享给金币时的金币数量</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+有效下级用户每笔有效下注获得此值的万分比提成奖励
+实际获得返利金额  =  有效下注金额 × 此值 ÷ 10000
+</t>
         </r>
       </text>
     </comment>
@@ -104,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="136">
   <si>
     <t>序列ID</t>
   </si>
@@ -124,7 +150,10 @@
     <t>奖励</t>
   </si>
   <si>
-    <t>收益比例</t>
+    <t>充值收益比例</t>
+  </si>
+  <si>
+    <t>有效下注的收益比例</t>
   </si>
   <si>
     <t>int</t>
@@ -152,6 +181,9 @@
   </si>
   <si>
     <t>proportion</t>
+  </si>
+  <si>
+    <t>betproportion</t>
   </si>
   <si>
     <t>档位1</t>
@@ -714,7 +746,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1189,25 +1221,25 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
@@ -1566,8 +1598,9 @@
     <col min="5" max="5" width="10.125" style="3" customWidth="1"/>
     <col min="6" max="6" width="19.5" style="4" customWidth="1"/>
     <col min="7" max="7" width="32.875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.625" style="3" customWidth="1"/>
-    <col min="9" max="10" width="9" style="3"/>
+    <col min="8" max="8" width="12.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="19.125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="9" style="3"/>
     <col min="11" max="11" width="9.25" style="3" customWidth="1"/>
     <col min="12" max="16384" width="9" style="3"/>
   </cols>
@@ -1595,49 +1628,58 @@
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="I1" s="7" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>9</v>
       </c>
+      <c r="G2" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="H2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="8" t="s">
         <v>14</v>
       </c>
+      <c r="G3" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="H3" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1649,1127 +1691,1278 @@
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
+      <c r="I4" s="7"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:11">
-      <c r="A5" s="9">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9">
-        <v>1</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="10">
+        <v>20</v>
+      </c>
+      <c r="I5" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:11">
+      <c r="A6" s="10">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10">
+        <v>1</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="11">
+        <v>12</v>
+      </c>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="10">
+        <v>40</v>
+      </c>
+      <c r="I6" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:11">
+      <c r="A7" s="10">
+        <v>3</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="10">
+        <v>24</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="10">
+        <v>60</v>
+      </c>
+      <c r="I7" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:11">
+      <c r="A8" s="11">
+        <v>4</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="10">
+        <v>1</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="11">
+        <v>36</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="10">
+        <v>80</v>
+      </c>
+      <c r="I8" s="10">
+        <v>20</v>
+      </c>
+      <c r="K8" s="12"/>
+    </row>
+    <row r="9" s="2" customFormat="1" spans="1:11">
+      <c r="A9" s="11">
+        <v>5</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="10">
+        <v>1</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="10">
+        <v>46</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="10">
+        <v>100</v>
+      </c>
+      <c r="I9" s="10">
+        <v>20</v>
+      </c>
+      <c r="K9" s="12"/>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:11">
+      <c r="A10" s="11">
+        <v>6</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="10">
+        <v>1</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="11">
+        <v>58</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="10">
+        <v>120</v>
+      </c>
+      <c r="I10" s="10">
+        <v>20</v>
+      </c>
+      <c r="K10" s="12"/>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="1:11">
+      <c r="A11" s="11">
+        <v>7</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="10">
+        <v>1</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="10">
+        <v>70</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="10">
+        <v>140</v>
+      </c>
+      <c r="I11" s="10">
+        <v>20</v>
+      </c>
+      <c r="K11" s="12"/>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:11">
+      <c r="A12" s="11">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="10">
+        <v>1</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="11">
+        <v>82</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="10">
+        <v>160</v>
+      </c>
+      <c r="I12" s="10">
+        <v>20</v>
+      </c>
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="1:11">
+      <c r="A13" s="11">
+        <v>9</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="10">
+        <v>1</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="10">
+        <v>94</v>
+      </c>
+      <c r="F13" s="13"/>
+      <c r="G13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="10">
+        <v>180</v>
+      </c>
+      <c r="I13" s="10">
+        <v>20</v>
+      </c>
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:11">
+      <c r="A14" s="11">
+        <v>10</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="10">
+        <v>1</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="10">
+        <v>105</v>
+      </c>
+      <c r="F14" s="13"/>
+      <c r="G14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="10">
+        <v>200</v>
+      </c>
+      <c r="I14" s="10">
+        <v>20</v>
+      </c>
+      <c r="K14" s="12"/>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:11">
+      <c r="A15" s="11">
+        <v>11</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11">
+        <v>1</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="11">
+        <v>120</v>
+      </c>
+      <c r="F15" s="13"/>
+      <c r="G15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="11">
+        <v>220</v>
+      </c>
+      <c r="I15" s="10">
+        <v>20</v>
+      </c>
+      <c r="K15" s="12"/>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:11">
+      <c r="A16" s="11">
+        <v>12</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11">
+        <v>1</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="11">
+        <v>140</v>
+      </c>
+      <c r="F16" s="13"/>
+      <c r="G16" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="11">
+        <v>240</v>
+      </c>
+      <c r="I16" s="10">
+        <v>20</v>
+      </c>
+      <c r="K16" s="12"/>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:11">
+      <c r="A17" s="11">
+        <v>13</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11">
+        <v>1</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="11">
+        <v>160</v>
+      </c>
+      <c r="F17" s="13"/>
+      <c r="G17" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="11">
+        <v>260</v>
+      </c>
+      <c r="I17" s="10">
+        <v>20</v>
+      </c>
+      <c r="K17" s="12"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="11">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11">
+        <v>1</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="11">
+        <v>180</v>
+      </c>
+      <c r="F18" s="13"/>
+      <c r="G18" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="11">
+        <v>280</v>
+      </c>
+      <c r="I18" s="10">
+        <v>20</v>
+      </c>
+      <c r="K18"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="11">
+        <v>15</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11">
+        <v>1</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="11">
+        <v>200</v>
+      </c>
+      <c r="F19" s="13"/>
+      <c r="G19" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="11">
+        <v>300</v>
+      </c>
+      <c r="I19" s="10">
+        <v>20</v>
+      </c>
+      <c r="K19"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="11">
         <v>16</v>
       </c>
-      <c r="E5" s="9">
-        <v>1</v>
-      </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9" t="s">
+      <c r="B20" s="11"/>
+      <c r="C20" s="11">
+        <v>1</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="11">
+        <v>220</v>
+      </c>
+      <c r="F20" s="13"/>
+      <c r="G20" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="11">
+        <v>320</v>
+      </c>
+      <c r="I20" s="10">
+        <v>20</v>
+      </c>
+      <c r="K20"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="11">
         <v>17</v>
       </c>
-      <c r="H5" s="9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:11">
-      <c r="A6" s="9">
-        <v>2</v>
-      </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9">
-        <v>1</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="B21" s="11"/>
+      <c r="C21" s="11">
+        <v>1</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="11">
+        <v>240</v>
+      </c>
+      <c r="F21" s="13"/>
+      <c r="G21" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H21" s="11">
+        <v>340</v>
+      </c>
+      <c r="I21" s="10">
+        <v>20</v>
+      </c>
+      <c r="K21"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="11">
         <v>18</v>
       </c>
-      <c r="E6" s="10">
-        <v>12</v>
-      </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9" t="s">
+      <c r="B22" s="11"/>
+      <c r="C22" s="11">
+        <v>1</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="11">
+        <v>260</v>
+      </c>
+      <c r="F22" s="13"/>
+      <c r="G22" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="11">
+        <v>360</v>
+      </c>
+      <c r="I22" s="10">
+        <v>20</v>
+      </c>
+      <c r="K22"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="11">
         <v>19</v>
       </c>
-      <c r="H6" s="9">
+      <c r="B23" s="11"/>
+      <c r="C23" s="11">
+        <v>1</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="11">
+        <v>280</v>
+      </c>
+      <c r="F23" s="14"/>
+      <c r="G23" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="11">
+        <v>380</v>
+      </c>
+      <c r="I23" s="10">
+        <v>20</v>
+      </c>
+      <c r="K23"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="11">
+        <v>20</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11">
+        <v>1</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="11">
+        <v>300</v>
+      </c>
+      <c r="F24" s="14"/>
+      <c r="G24" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H24" s="11">
+        <v>400</v>
+      </c>
+      <c r="I24" s="10">
+        <v>20</v>
+      </c>
+      <c r="K24"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="11">
+        <v>21</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11">
+        <v>1</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" s="11">
+        <v>340</v>
+      </c>
+      <c r="F25" s="14"/>
+      <c r="G25" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" s="11">
+        <v>420</v>
+      </c>
+      <c r="I25" s="10">
+        <v>20</v>
+      </c>
+      <c r="K25"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="11">
+        <v>22</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11">
+        <v>1</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="11">
+        <v>380</v>
+      </c>
+      <c r="F26" s="14"/>
+      <c r="G26" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H26" s="11">
+        <v>440</v>
+      </c>
+      <c r="I26" s="10">
+        <v>20</v>
+      </c>
+      <c r="K26"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="11">
+        <v>23</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11">
+        <v>1</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="11">
+        <v>420</v>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="G27" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H27" s="11">
+        <v>460</v>
+      </c>
+      <c r="I27" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="11">
+        <v>24</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11">
+        <v>1</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="11">
+        <v>460</v>
+      </c>
+      <c r="F28" s="14"/>
+      <c r="G28" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H28" s="11">
+        <v>480</v>
+      </c>
+      <c r="I28" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="11">
+        <v>25</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11">
+        <v>1</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" s="11">
+        <v>500</v>
+      </c>
+      <c r="F29" s="14"/>
+      <c r="G29" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H29" s="11">
+        <v>500</v>
+      </c>
+      <c r="I29" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="11">
+        <v>26</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11">
+        <v>1</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="11">
+        <v>540</v>
+      </c>
+      <c r="F30" s="14"/>
+      <c r="G30" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H30" s="11">
+        <v>520</v>
+      </c>
+      <c r="I30" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="11">
+        <v>27</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11">
+        <v>1</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="11">
+        <v>580</v>
+      </c>
+      <c r="F31" s="14"/>
+      <c r="G31" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H31" s="11">
+        <v>540</v>
+      </c>
+      <c r="I31" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="11">
+        <v>28</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11">
+        <v>1</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E32" s="11">
+        <v>620</v>
+      </c>
+      <c r="F32" s="14"/>
+      <c r="G32" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="H32" s="11">
+        <v>560</v>
+      </c>
+      <c r="I32" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="11">
+        <v>29</v>
+      </c>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11">
+        <v>1</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" s="11">
+        <v>660</v>
+      </c>
+      <c r="F33" s="14"/>
+      <c r="G33" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H33" s="11">
+        <v>580</v>
+      </c>
+      <c r="I33" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="11">
+        <v>30</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11">
+        <v>1</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" s="11">
+        <v>700</v>
+      </c>
+      <c r="F34" s="14"/>
+      <c r="G34" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H34" s="11">
+        <v>600</v>
+      </c>
+      <c r="I34" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="11">
+        <v>31</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11">
+        <v>1</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="11">
+        <v>780</v>
+      </c>
+      <c r="F35" s="14"/>
+      <c r="G35" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H35" s="11">
+        <v>620</v>
+      </c>
+      <c r="I35" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="11">
+        <v>32</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11">
+        <v>1</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" s="11">
+        <v>860</v>
+      </c>
+      <c r="F36" s="14"/>
+      <c r="G36" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H36" s="11">
+        <v>640</v>
+      </c>
+      <c r="I36" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="11">
+        <v>33</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11">
+        <v>1</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E37" s="11">
+        <v>940</v>
+      </c>
+      <c r="F37" s="14"/>
+      <c r="G37" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H37" s="11">
+        <v>660</v>
+      </c>
+      <c r="I37" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="11">
+        <v>34</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11">
+        <v>1</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" s="11">
+        <v>1020</v>
+      </c>
+      <c r="F38" s="14"/>
+      <c r="G38" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="H38" s="11">
+        <v>680</v>
+      </c>
+      <c r="I38" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="11">
+        <v>35</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11">
+        <v>1</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E39" s="11">
+        <v>1100</v>
+      </c>
+      <c r="F39" s="14"/>
+      <c r="G39" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="H39" s="11">
+        <v>700</v>
+      </c>
+      <c r="I39" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="11">
+        <v>36</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11">
+        <v>1</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E40" s="11">
+        <v>1180</v>
+      </c>
+      <c r="F40" s="14"/>
+      <c r="G40" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="H40" s="11">
+        <v>720</v>
+      </c>
+      <c r="I40" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="11">
+        <v>37</v>
+      </c>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11">
+        <v>1</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E41" s="11">
+        <v>1260</v>
+      </c>
+      <c r="F41" s="14"/>
+      <c r="G41" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="H41" s="11">
+        <v>740</v>
+      </c>
+      <c r="I41" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="11">
+        <v>38</v>
+      </c>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11">
+        <v>1</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E42" s="11">
+        <v>1340</v>
+      </c>
+      <c r="F42" s="14"/>
+      <c r="G42" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="H42" s="11">
+        <v>760</v>
+      </c>
+      <c r="I42" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="11">
+        <v>39</v>
+      </c>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11">
+        <v>1</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E43" s="11">
+        <v>1420</v>
+      </c>
+      <c r="F43" s="14"/>
+      <c r="G43" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H43" s="11">
+        <v>780</v>
+      </c>
+      <c r="I43" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="11">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:11">
-      <c r="A7" s="9">
-        <v>3</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9">
-        <v>1</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="9">
-        <v>24</v>
-      </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="9">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:11">
-      <c r="A8" s="10">
-        <v>4</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="9">
-        <v>1</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="10">
-        <v>36</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="9">
-        <v>80</v>
-      </c>
-      <c r="K8" s="11"/>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:11">
-      <c r="A9" s="10">
-        <v>5</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="9">
-        <v>1</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="B44" s="11"/>
+      <c r="C44" s="11">
+        <v>1</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E44" s="11">
+        <v>1500</v>
+      </c>
+      <c r="F44" s="14"/>
+      <c r="G44" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="H44" s="11">
+        <v>800</v>
+      </c>
+      <c r="I44" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="11">
+        <v>41</v>
+      </c>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11">
+        <v>1</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E45" s="11">
+        <v>1670</v>
+      </c>
+      <c r="F45" s="14"/>
+      <c r="G45" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="H45" s="11">
+        <v>820</v>
+      </c>
+      <c r="I45" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="11">
+        <v>42</v>
+      </c>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11">
+        <v>1</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E46" s="11">
+        <v>1840</v>
+      </c>
+      <c r="F46" s="14"/>
+      <c r="G46" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="H46" s="11">
+        <v>840</v>
+      </c>
+      <c r="I46" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="11">
+        <v>43</v>
+      </c>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11">
+        <v>1</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E47" s="11">
+        <v>2010</v>
+      </c>
+      <c r="F47" s="14"/>
+      <c r="G47" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H47" s="11">
+        <v>860</v>
+      </c>
+      <c r="I47" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="11">
+        <v>44</v>
+      </c>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11">
+        <v>1</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E48" s="11">
+        <v>2180</v>
+      </c>
+      <c r="F48" s="14"/>
+      <c r="G48" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="H48" s="11">
+        <v>880</v>
+      </c>
+      <c r="I48" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="11">
+        <v>45</v>
+      </c>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11">
+        <v>1</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E49" s="11">
+        <v>2350</v>
+      </c>
+      <c r="F49" s="14"/>
+      <c r="G49" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="H49" s="11">
+        <v>900</v>
+      </c>
+      <c r="I49" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="11">
         <v>46</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="9">
-        <v>100</v>
-      </c>
-      <c r="K9" s="11"/>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:11">
-      <c r="A10" s="10">
-        <v>6</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="9">
-        <v>1</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="10">
-        <v>58</v>
-      </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="9">
-        <v>120</v>
-      </c>
-      <c r="K10" s="11"/>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:11">
-      <c r="A11" s="10">
-        <v>7</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="9">
-        <v>1</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="9">
-        <v>70</v>
-      </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="9">
-        <v>140</v>
-      </c>
-      <c r="K11" s="11"/>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:11">
-      <c r="A12" s="10">
-        <v>8</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="9">
-        <v>1</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="10">
-        <v>82</v>
-      </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="9">
-        <v>160</v>
-      </c>
-      <c r="K12" s="11"/>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:11">
-      <c r="A13" s="10">
-        <v>9</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="9">
-        <v>1</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="9">
-        <v>94</v>
-      </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="9">
-        <v>180</v>
-      </c>
-      <c r="K13" s="11"/>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:11">
-      <c r="A14" s="10">
-        <v>10</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="9">
-        <v>1</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="9">
-        <v>105</v>
-      </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" s="9">
-        <v>200</v>
-      </c>
-      <c r="K14" s="11"/>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:11">
-      <c r="A15" s="10">
-        <v>11</v>
-      </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10">
-        <v>1</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="10">
-        <v>120</v>
-      </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="10">
-        <v>220</v>
-      </c>
-      <c r="K15" s="11"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:11">
-      <c r="A16" s="10">
-        <v>12</v>
-      </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10">
-        <v>1</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" s="10">
-        <v>140</v>
-      </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" s="10">
-        <v>240</v>
-      </c>
-      <c r="K16" s="11"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:11">
-      <c r="A17" s="10">
-        <v>13</v>
-      </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10">
-        <v>1</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="10">
-        <v>160</v>
-      </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H17" s="10">
-        <v>260</v>
-      </c>
-      <c r="K17" s="11"/>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="10">
-        <v>14</v>
-      </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10">
-        <v>1</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="10">
-        <v>180</v>
-      </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="10">
-        <v>280</v>
-      </c>
-      <c r="K18"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="10">
-        <v>15</v>
-      </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10">
-        <v>1</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="10">
-        <v>200</v>
-      </c>
-      <c r="F19" s="12"/>
-      <c r="G19" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="H19" s="10">
-        <v>300</v>
-      </c>
-      <c r="K19"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="10">
-        <v>16</v>
-      </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10">
-        <v>1</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20" s="10">
-        <v>220</v>
-      </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="9" t="s">
+      <c r="B50" s="11"/>
+      <c r="C50" s="11">
+        <v>1</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="E50" s="11">
+        <v>2520</v>
+      </c>
+      <c r="F50" s="14"/>
+      <c r="G50" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H50" s="11">
+        <v>920</v>
+      </c>
+      <c r="I50" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="11">
         <v>47</v>
       </c>
-      <c r="H20" s="10">
-        <v>320</v>
-      </c>
-      <c r="K20"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="10">
-        <v>17</v>
-      </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10">
-        <v>1</v>
-      </c>
-      <c r="D21" s="10" t="s">
+      <c r="B51" s="11"/>
+      <c r="C51" s="11">
+        <v>1</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E51" s="11">
+        <v>2690</v>
+      </c>
+      <c r="F51" s="14"/>
+      <c r="G51" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="H51" s="11">
+        <v>940</v>
+      </c>
+      <c r="I51" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="11">
         <v>48</v>
       </c>
-      <c r="E21" s="10">
-        <v>240</v>
-      </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="9" t="s">
+      <c r="B52" s="11"/>
+      <c r="C52" s="11">
+        <v>1</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E52" s="11">
+        <v>2860</v>
+      </c>
+      <c r="F52" s="14"/>
+      <c r="G52" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="H52" s="11">
+        <v>960</v>
+      </c>
+      <c r="I52" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="11">
         <v>49</v>
       </c>
-      <c r="H21" s="10">
-        <v>340</v>
-      </c>
-      <c r="K21"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="10">
-        <v>18</v>
-      </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10">
-        <v>1</v>
-      </c>
-      <c r="D22" s="10" t="s">
+      <c r="B53" s="11"/>
+      <c r="C53" s="11">
+        <v>1</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E53" s="11">
+        <v>3030</v>
+      </c>
+      <c r="F53" s="14"/>
+      <c r="G53" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H53" s="11">
+        <v>980</v>
+      </c>
+      <c r="I53" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="11">
         <v>50</v>
       </c>
-      <c r="E22" s="10">
-        <v>260</v>
-      </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H22" s="10">
-        <v>360</v>
-      </c>
-      <c r="K22"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="13">
-        <v>19</v>
-      </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13">
-        <v>1</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="13">
-        <v>280</v>
-      </c>
-      <c r="F23" s="14"/>
-      <c r="G23" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="H23" s="13">
-        <v>380</v>
-      </c>
-      <c r="K23"/>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="13">
-        <v>20</v>
-      </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13">
-        <v>1</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24" s="13">
-        <v>300</v>
-      </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="H24" s="13">
-        <v>400</v>
-      </c>
-      <c r="K24"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="13">
-        <v>21</v>
-      </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13">
-        <v>1</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E25" s="13">
-        <v>340</v>
-      </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="H25" s="13">
-        <v>420</v>
-      </c>
-      <c r="K25"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="13">
-        <v>22</v>
-      </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13">
-        <v>1</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E26" s="13">
-        <v>380</v>
-      </c>
-      <c r="F26" s="14"/>
-      <c r="G26" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="H26" s="13">
-        <v>440</v>
-      </c>
-      <c r="K26"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="13">
-        <v>23</v>
-      </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E27" s="13">
-        <v>420</v>
-      </c>
-      <c r="F27" s="14"/>
-      <c r="G27" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H27" s="13">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="13">
-        <v>24</v>
-      </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E28" s="13">
-        <v>460</v>
-      </c>
-      <c r="F28" s="14"/>
-      <c r="G28" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="H28" s="13">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="13">
-        <v>25</v>
-      </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13">
-        <v>1</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E29" s="13">
-        <v>500</v>
-      </c>
-      <c r="F29" s="14"/>
-      <c r="G29" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="H29" s="13">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="13">
-        <v>26</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13">
-        <v>1</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" s="13">
-        <v>540</v>
-      </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H30" s="13">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="13">
-        <v>27</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13">
-        <v>1</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E31" s="13">
-        <v>580</v>
-      </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="H31" s="13">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="13">
-        <v>28</v>
-      </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13">
-        <v>1</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E32" s="13">
-        <v>620</v>
-      </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="H32" s="13">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="13">
-        <v>29</v>
-      </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13">
-        <v>1</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E33" s="13">
-        <v>660</v>
-      </c>
-      <c r="F33" s="14"/>
-      <c r="G33" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="H33" s="13">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="13">
-        <v>30</v>
-      </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13">
-        <v>1</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" s="13">
-        <v>700</v>
-      </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="H34" s="13">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="13">
-        <v>31</v>
-      </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13">
-        <v>1</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E35" s="13">
-        <v>780</v>
-      </c>
-      <c r="F35" s="14"/>
-      <c r="G35" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="H35" s="13">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="13">
-        <v>32</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13">
-        <v>1</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="E36" s="13">
-        <v>860</v>
-      </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="H36" s="13">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="13">
-        <v>33</v>
-      </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13">
-        <v>1</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="E37" s="13">
-        <v>940</v>
-      </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H37" s="13">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="13">
-        <v>34</v>
-      </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13">
-        <v>1</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E38" s="13">
-        <v>1020</v>
-      </c>
-      <c r="F38" s="14"/>
-      <c r="G38" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="H38" s="13">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="13">
-        <v>35</v>
-      </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13">
-        <v>1</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="E39" s="13">
-        <v>1100</v>
-      </c>
-      <c r="F39" s="14"/>
-      <c r="G39" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="H39" s="13">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="13">
-        <v>36</v>
-      </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13">
-        <v>1</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E40" s="13">
-        <v>1180</v>
-      </c>
-      <c r="F40" s="14"/>
-      <c r="G40" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="H40" s="13">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="13">
-        <v>37</v>
-      </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13">
-        <v>1</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E41" s="13">
-        <v>1260</v>
-      </c>
-      <c r="F41" s="14"/>
-      <c r="G41" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="H41" s="13">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="13">
-        <v>38</v>
-      </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13">
-        <v>1</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E42" s="13">
-        <v>1340</v>
-      </c>
-      <c r="F42" s="14"/>
-      <c r="G42" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="H42" s="13">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="13">
-        <v>39</v>
-      </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13">
-        <v>1</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E43" s="13">
-        <v>1420</v>
-      </c>
-      <c r="F43" s="14"/>
-      <c r="G43" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="H43" s="13">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="13">
-        <v>40</v>
-      </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13">
-        <v>1</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="E44" s="13">
-        <v>1500</v>
-      </c>
-      <c r="F44" s="14"/>
-      <c r="G44" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="H44" s="13">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="13">
-        <v>41</v>
-      </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13">
-        <v>1</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="E45" s="13">
-        <v>1670</v>
-      </c>
-      <c r="F45" s="14"/>
-      <c r="G45" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="H45" s="13">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="13">
-        <v>42</v>
-      </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13">
-        <v>1</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E46" s="13">
-        <v>1840</v>
-      </c>
-      <c r="F46" s="14"/>
-      <c r="G46" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="H46" s="13">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="13">
-        <v>43</v>
-      </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13">
-        <v>1</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E47" s="13">
-        <v>2010</v>
-      </c>
-      <c r="F47" s="14"/>
-      <c r="G47" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H47" s="13">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="13">
-        <v>44</v>
-      </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13">
-        <v>1</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E48" s="13">
-        <v>2180</v>
-      </c>
-      <c r="F48" s="14"/>
-      <c r="G48" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="H48" s="13">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="13">
-        <v>45</v>
-      </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13">
-        <v>1</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E49" s="13">
-        <v>2350</v>
-      </c>
-      <c r="F49" s="14"/>
-      <c r="G49" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="H49" s="13">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="13">
-        <v>46</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13">
-        <v>1</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E50" s="13">
-        <v>2520</v>
-      </c>
-      <c r="F50" s="14"/>
-      <c r="G50" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="H50" s="13">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="13">
-        <v>47</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13">
-        <v>1</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E51" s="13">
-        <v>2690</v>
-      </c>
-      <c r="F51" s="14"/>
-      <c r="G51" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="H51" s="13">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="13">
-        <v>48</v>
-      </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13">
-        <v>1</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="E52" s="13">
-        <v>2860</v>
-      </c>
-      <c r="F52" s="14"/>
-      <c r="G52" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="H52" s="13">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="13">
-        <v>49</v>
-      </c>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13">
-        <v>1</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="E53" s="13">
-        <v>3030</v>
-      </c>
-      <c r="F53" s="14"/>
-      <c r="G53" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="H53" s="13">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="13">
-        <v>50</v>
-      </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13">
-        <v>1</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E54" s="13">
+      <c r="B54" s="11"/>
+      <c r="C54" s="11">
+        <v>1</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E54" s="11">
         <v>3200</v>
       </c>
       <c r="F54" s="14"/>
-      <c r="G54" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="H54" s="13">
+      <c r="G54" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="H54" s="11">
         <v>1000</v>
       </c>
-    </row>
-    <row r="55" spans="1:8">
+      <c r="I54" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="15">
         <v>101</v>
       </c>
@@ -2778,18 +2971,19 @@
         <v>2</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E55" s="15"/>
       <c r="F55" s="16">
         <v>1</v>
       </c>
       <c r="G55" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H55" s="15"/>
-    </row>
-    <row r="56" spans="1:8">
+      <c r="I55" s="15"/>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="15">
         <v>102</v>
       </c>
@@ -2798,18 +2992,19 @@
         <v>2</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="16">
         <v>2</v>
       </c>
       <c r="G56" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H56" s="15"/>
-    </row>
-    <row r="57" spans="1:8">
+      <c r="I56" s="15"/>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="15">
         <v>103</v>
       </c>
@@ -2818,18 +3013,19 @@
         <v>2</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="16">
         <v>3</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H57" s="15"/>
-    </row>
-    <row r="58" spans="1:8">
+      <c r="I57" s="15"/>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="15">
         <v>104</v>
       </c>
@@ -2838,18 +3034,19 @@
         <v>2</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="16">
         <v>4</v>
       </c>
       <c r="G58" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H58" s="15"/>
-    </row>
-    <row r="59" spans="1:8">
+      <c r="I58" s="15"/>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="15">
         <v>105</v>
       </c>
@@ -2858,18 +3055,19 @@
         <v>2</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="16">
         <v>5</v>
       </c>
       <c r="G59" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H59" s="15"/>
-    </row>
-    <row r="60" spans="1:8">
+      <c r="I59" s="15"/>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="15">
         <v>106</v>
       </c>
@@ -2878,18 +3076,19 @@
         <v>2</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="16" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G60" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H60" s="15"/>
-    </row>
-    <row r="61" spans="1:8">
+      <c r="I60" s="15"/>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="15">
         <v>107</v>
       </c>
@@ -2898,18 +3097,19 @@
         <v>2</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E61" s="15"/>
       <c r="F61" s="16" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G61" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H61" s="15"/>
-    </row>
-    <row r="62" spans="1:8">
+      <c r="I61" s="15"/>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="15">
         <v>108</v>
       </c>
@@ -2918,16 +3118,17 @@
         <v>2</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="16" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G62" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/poker/resources/sample/SharePromote.xlsx
+++ b/poker/resources/sample/SharePromote.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="SharePromote" sheetId="1" r:id="rId1"/>
@@ -130,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
   <si>
     <t>序列ID</t>
   </si>
@@ -210,31 +210,40 @@
     <t>1990000_1200000</t>
   </si>
   <si>
+    <t>档位5</t>
+  </si>
+  <si>
+    <t>1990000_3000000</t>
+  </si>
+  <si>
     <t>排名1</t>
   </si>
   <si>
-    <t>1990000_2250000</t>
+    <t>1990000_1125000</t>
   </si>
   <si>
     <t>排名2</t>
   </si>
   <si>
-    <t>1990000_1650000</t>
+    <t>1990000_825000</t>
   </si>
   <si>
     <t>排名3</t>
   </si>
   <si>
+    <t>1990000_600000</t>
+  </si>
+  <si>
     <t>排名4</t>
   </si>
   <si>
-    <t>1990000_900000</t>
+    <t>1990000_450000</t>
   </si>
   <si>
     <t>排名5</t>
   </si>
   <si>
-    <t>1990000_600000</t>
+    <t>1990000_300000</t>
   </si>
   <si>
     <t>排名6-10</t>
@@ -243,25 +252,25 @@
     <t>6_10</t>
   </si>
   <si>
-    <t>1990000_300000</t>
-  </si>
-  <si>
-    <t>排名11-50</t>
+    <t>1990000_150000</t>
+  </si>
+  <si>
+    <t>排名11-20</t>
   </si>
   <si>
     <t>11_20</t>
   </si>
   <si>
-    <t>1990000_225000</t>
-  </si>
-  <si>
-    <t>排名51-100</t>
+    <t>1990000_112000</t>
+  </si>
+  <si>
+    <t>排名21-50</t>
   </si>
   <si>
     <t>21_50</t>
   </si>
   <si>
-    <t>1990000_150000</t>
+    <t>1990000_75000</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1317,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="7" style="3" customWidth="1"/>
@@ -1433,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="10">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:11">
@@ -1458,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="10">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:11">
@@ -1508,34 +1517,39 @@
         <v>0</v>
       </c>
       <c r="I8" s="10">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K8" s="12"/>
     </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="13">
-        <v>101</v>
-      </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13">
-        <v>2</v>
-      </c>
-      <c r="D9" s="13" t="s">
+    <row r="9" s="2" customFormat="1" spans="1:11">
+      <c r="A9" s="11">
+        <v>5</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="10">
+        <v>1</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="14">
-        <v>1</v>
-      </c>
-      <c r="G9" s="13" t="s">
+      <c r="E9" s="11">
+        <v>500</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
+      <c r="H9" s="10">
+        <v>0</v>
+      </c>
+      <c r="I9" s="10">
+        <v>50</v>
+      </c>
+      <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="13">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13">
@@ -1546,7 +1560,7 @@
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>29</v>
@@ -1556,7 +1570,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="13">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13">
@@ -1567,70 +1581,70 @@
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="13">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13">
         <v>2</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="13">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13">
         <v>2</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="13">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13">
         <v>2</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" s="13"/>
-      <c r="F14" s="14" t="s">
-        <v>36</v>
+      <c r="F14" s="14">
+        <v>5</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>37</v>
@@ -1640,7 +1654,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="13">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13">
@@ -1661,7 +1675,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="13">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13">
@@ -1679,6 +1693,27 @@
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="13">
+        <v>108</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13">
+        <v>2</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="13"/>
+      <c r="F17" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/poker/resources/sample/SharePromote.xlsx
+++ b/poker/resources/sample/SharePromote.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SharePromote" sheetId="1" r:id="rId1"/>
@@ -219,31 +219,31 @@
     <t>排名1</t>
   </si>
   <si>
-    <t>1990000_1125000</t>
+    <t>1990000_1500000</t>
   </si>
   <si>
     <t>排名2</t>
   </si>
   <si>
-    <t>1990000_825000</t>
+    <t>1990000_1000000</t>
   </si>
   <si>
     <t>排名3</t>
   </si>
   <si>
+    <t>1990000_800000</t>
+  </si>
+  <si>
+    <t>排名4</t>
+  </si>
+  <si>
     <t>1990000_600000</t>
   </si>
   <si>
-    <t>排名4</t>
-  </si>
-  <si>
-    <t>1990000_450000</t>
-  </si>
-  <si>
     <t>排名5</t>
   </si>
   <si>
-    <t>1990000_300000</t>
+    <t>1990000_400000</t>
   </si>
   <si>
     <t>排名6-10</t>
@@ -252,7 +252,7 @@
     <t>6_10</t>
   </si>
   <si>
-    <t>1990000_150000</t>
+    <t>1990000_200000</t>
   </si>
   <si>
     <t>排名11-20</t>
@@ -261,7 +261,7 @@
     <t>11_20</t>
   </si>
   <si>
-    <t>1990000_112000</t>
+    <t>1990000_120000</t>
   </si>
   <si>
     <t>排名21-50</t>
@@ -270,7 +270,7 @@
     <t>21_50</t>
   </si>
   <si>
-    <t>1990000_75000</t>
+    <t>1990000_100000</t>
   </si>
 </sst>
 </file>
@@ -453,12 +453,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -932,7 +932,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -967,9 +967,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1317,7 +1314,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="7" style="3" customWidth="1"/>
@@ -1329,10 +1326,12 @@
     <col min="9" max="9" width="19.125" style="3" customWidth="1"/>
     <col min="10" max="10" width="9" style="3"/>
     <col min="11" max="11" width="9.25" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="3"/>
+    <col min="12" max="12" width="11.625" style="3"/>
+    <col min="13" max="13" width="14.125" style="3"/>
+    <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1359,7 +1358,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
@@ -1384,7 +1383,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:13">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1409,7 +1408,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:13">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -1420,7 +1419,7 @@
       <c r="H4" s="5"/>
       <c r="I4" s="7"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:11">
+    <row r="5" s="1" customFormat="1" spans="1:13">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -1444,8 +1443,9 @@
       <c r="I5" s="10">
         <v>30</v>
       </c>
+      <c r="M5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:11">
+    <row r="6" s="1" customFormat="1" spans="1:13">
       <c r="A6" s="10">
         <v>2</v>
       </c>
@@ -1469,8 +1469,9 @@
       <c r="I6" s="10">
         <v>35</v>
       </c>
+      <c r="M6" s="2"/>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:11">
+    <row r="7" s="1" customFormat="1" spans="1:13">
       <c r="A7" s="10">
         <v>3</v>
       </c>
@@ -1494,8 +1495,9 @@
       <c r="I7" s="10">
         <v>40</v>
       </c>
+      <c r="M7" s="2"/>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:11">
+    <row r="8" s="2" customFormat="1" spans="1:13">
       <c r="A8" s="11">
         <v>4</v>
       </c>
@@ -1519,9 +1521,10 @@
       <c r="I8" s="10">
         <v>45</v>
       </c>
-      <c r="K8" s="12"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:11">
+    <row r="9" s="2" customFormat="1" spans="1:13">
       <c r="A9" s="11">
         <v>5</v>
       </c>
@@ -1545,175 +1548,176 @@
       <c r="I9" s="10">
         <v>50</v>
       </c>
-      <c r="K9" s="12"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
     </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="13">
+    <row r="10" spans="1:13">
+      <c r="A10" s="12">
         <v>101</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13">
+      <c r="B10" s="12"/>
+      <c r="C10" s="12">
         <v>2</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="14">
+      <c r="E10" s="12"/>
+      <c r="F10" s="13">
         <v>1</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
     </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="13">
+    <row r="11" spans="1:13">
+      <c r="A11" s="12">
         <v>102</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13">
+      <c r="B11" s="12"/>
+      <c r="C11" s="12">
         <v>2</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="14">
+      <c r="E11" s="12"/>
+      <c r="F11" s="13">
         <v>2</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
     </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="13">
+    <row r="12" spans="1:13">
+      <c r="A12" s="12">
         <v>103</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12">
         <v>2</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="14">
+      <c r="E12" s="12"/>
+      <c r="F12" s="13">
         <v>3</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
     </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="13">
+    <row r="13" spans="1:13">
+      <c r="A13" s="12">
         <v>104</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13">
+      <c r="B13" s="12"/>
+      <c r="C13" s="12">
         <v>2</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="14">
+      <c r="E13" s="12"/>
+      <c r="F13" s="13">
         <v>4</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
     </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="13">
+    <row r="14" spans="1:13">
+      <c r="A14" s="12">
         <v>105</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12">
         <v>2</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="14">
+      <c r="E14" s="12"/>
+      <c r="F14" s="13">
         <v>5</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
     </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="13">
+    <row r="15" spans="1:13">
+      <c r="A15" s="12">
         <v>106</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12">
         <v>2</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="14" t="s">
+      <c r="E15" s="12"/>
+      <c r="F15" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
     </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="13">
+    <row r="16" spans="1:13">
+      <c r="A16" s="12">
         <v>107</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13">
+      <c r="B16" s="12"/>
+      <c r="C16" s="12">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="14" t="s">
+      <c r="E16" s="12"/>
+      <c r="F16" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="13">
+      <c r="A17" s="12">
         <v>108</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12">
         <v>2</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="14" t="s">
+      <c r="E17" s="12"/>
+      <c r="F17" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/poker/resources/sample/SharePromote.xlsx
+++ b/poker/resources/sample/SharePromote.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="SharePromote" sheetId="1" r:id="rId1"/>
@@ -189,49 +189,49 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_10000</t>
+    <t>1990000_84000</t>
   </si>
   <si>
     <t>档位2</t>
   </si>
   <si>
-    <t>1990000_90000</t>
+    <t>1990000_756000</t>
   </si>
   <si>
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_700000</t>
+    <t>1990000_5880000</t>
   </si>
   <si>
     <t>档位4</t>
   </si>
   <si>
+    <t>1990000_10080000</t>
+  </si>
+  <si>
+    <t>档位5</t>
+  </si>
+  <si>
+    <t>1990000_25200000</t>
+  </si>
+  <si>
+    <t>排名1</t>
+  </si>
+  <si>
+    <t>1990000_1500000</t>
+  </si>
+  <si>
+    <t>排名2</t>
+  </si>
+  <si>
     <t>1990000_1200000</t>
   </si>
   <si>
-    <t>档位5</t>
-  </si>
-  <si>
-    <t>1990000_3000000</t>
-  </si>
-  <si>
-    <t>排名1</t>
-  </si>
-  <si>
-    <t>1990000_1500000</t>
-  </si>
-  <si>
-    <t>排名2</t>
-  </si>
-  <si>
-    <t>1990000_1000000</t>
-  </si>
-  <si>
     <t>排名3</t>
   </si>
   <si>
-    <t>1990000_800000</t>
+    <t>1990000_900000</t>
   </si>
   <si>
     <t>排名4</t>
@@ -243,7 +243,7 @@
     <t>排名5</t>
   </si>
   <si>
-    <t>1990000_400000</t>
+    <t>1990000_450000</t>
   </si>
   <si>
     <t>排名6-10</t>
@@ -252,7 +252,7 @@
     <t>6_10</t>
   </si>
   <si>
-    <t>1990000_200000</t>
+    <t>1990000_390000</t>
   </si>
   <si>
     <t>排名11-20</t>
@@ -261,7 +261,7 @@
     <t>11_20</t>
   </si>
   <si>
-    <t>1990000_120000</t>
+    <t>1990000_300000</t>
   </si>
   <si>
     <t>排名21-50</t>
@@ -270,7 +270,7 @@
     <t>21_50</t>
   </si>
   <si>
-    <t>1990000_100000</t>
+    <t>1990000_180000</t>
   </si>
 </sst>
 </file>
@@ -453,12 +453,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="10">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="M5" s="2"/>
     </row>
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="10">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="M6" s="2"/>
     </row>
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="10">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="M7" s="2"/>
     </row>
@@ -1519,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="10">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1546,7 +1546,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="10">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>

--- a/poker/resources/sample/SharePromote.xlsx
+++ b/poker/resources/sample/SharePromote.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SharePromote" sheetId="1" r:id="rId1"/>
@@ -189,31 +189,31 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_84000</t>
+    <t>1990000_10000</t>
   </si>
   <si>
     <t>档位2</t>
   </si>
   <si>
-    <t>1990000_756000</t>
+    <t>1990000_90000</t>
   </si>
   <si>
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_5880000</t>
+    <t>1990000_700000</t>
   </si>
   <si>
     <t>档位4</t>
   </si>
   <si>
-    <t>1990000_10080000</t>
+    <t>1990000_1200000</t>
   </si>
   <si>
     <t>档位5</t>
   </si>
   <si>
-    <t>1990000_25200000</t>
+    <t>1990000_3000000</t>
   </si>
   <si>
     <t>排名1</t>
@@ -225,13 +225,13 @@
     <t>排名2</t>
   </si>
   <si>
-    <t>1990000_1200000</t>
+    <t>1990000_1000000</t>
   </si>
   <si>
     <t>排名3</t>
   </si>
   <si>
-    <t>1990000_900000</t>
+    <t>1990000_800000</t>
   </si>
   <si>
     <t>排名4</t>
@@ -243,7 +243,7 @@
     <t>排名5</t>
   </si>
   <si>
-    <t>1990000_450000</t>
+    <t>1990000_400000</t>
   </si>
   <si>
     <t>排名6-10</t>
@@ -252,7 +252,7 @@
     <t>6_10</t>
   </si>
   <si>
-    <t>1990000_390000</t>
+    <t>1990000_200000</t>
   </si>
   <si>
     <t>排名11-20</t>
@@ -261,7 +261,7 @@
     <t>11_20</t>
   </si>
   <si>
-    <t>1990000_300000</t>
+    <t>1990000_120000</t>
   </si>
   <si>
     <t>排名21-50</t>
@@ -270,7 +270,7 @@
     <t>21_50</t>
   </si>
   <si>
-    <t>1990000_180000</t>
+    <t>1990000_100000</t>
   </si>
 </sst>
 </file>
@@ -453,12 +453,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="10">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="M5" s="2"/>
     </row>
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="10">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="M6" s="2"/>
     </row>
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="10">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="M7" s="2"/>
     </row>
@@ -1519,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="10">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1546,7 +1546,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="10">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>

--- a/poker/resources/sample/SharePromote.xlsx
+++ b/poker/resources/sample/SharePromote.xlsx
@@ -189,61 +189,61 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_84000</t>
+    <t>1990000_420000</t>
   </si>
   <si>
     <t>档位2</t>
   </si>
   <si>
-    <t>1990000_756000</t>
+    <t>1990000_3780000</t>
   </si>
   <si>
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_5880000</t>
+    <t>1990000_29400000</t>
   </si>
   <si>
     <t>档位4</t>
   </si>
   <si>
-    <t>1990000_10080000</t>
+    <t>1990000_50400000</t>
   </si>
   <si>
     <t>档位5</t>
   </si>
   <si>
-    <t>1990000_25200000</t>
+    <t>1990000_126000000</t>
   </si>
   <si>
     <t>排名1</t>
   </si>
   <si>
-    <t>1990000_1500000</t>
+    <t>1990000_157500000</t>
   </si>
   <si>
     <t>排名2</t>
   </si>
   <si>
-    <t>1990000_1200000</t>
+    <t>1990000_120000000</t>
   </si>
   <si>
     <t>排名3</t>
   </si>
   <si>
-    <t>1990000_900000</t>
+    <t>1990000_82500000</t>
   </si>
   <si>
     <t>排名4</t>
   </si>
   <si>
-    <t>1990000_600000</t>
+    <t>1990000_52500000</t>
   </si>
   <si>
     <t>排名5</t>
   </si>
   <si>
-    <t>1990000_450000</t>
+    <t>1990000_30000000</t>
   </si>
   <si>
     <t>排名6-10</t>
@@ -252,7 +252,7 @@
     <t>6_10</t>
   </si>
   <si>
-    <t>1990000_390000</t>
+    <t>1990000_19500000</t>
   </si>
   <si>
     <t>排名11-20</t>
@@ -261,7 +261,7 @@
     <t>11_20</t>
   </si>
   <si>
-    <t>1990000_300000</t>
+    <t>1990000_7500000</t>
   </si>
   <si>
     <t>排名21-50</t>
@@ -270,7 +270,7 @@
     <t>21_50</t>
   </si>
   <si>
-    <t>1990000_180000</t>
+    <t>1990000_4500000</t>
   </si>
 </sst>
 </file>

--- a/poker/resources/sample/SharePromote.xlsx
+++ b/poker/resources/sample/SharePromote.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="SharePromote" sheetId="1" r:id="rId1"/>
@@ -189,61 +189,61 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_10000</t>
+    <t>1990000_420000</t>
   </si>
   <si>
     <t>档位2</t>
   </si>
   <si>
-    <t>1990000_90000</t>
+    <t>1990000_3780000</t>
   </si>
   <si>
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_700000</t>
+    <t>1990000_29400000</t>
   </si>
   <si>
     <t>档位4</t>
   </si>
   <si>
-    <t>1990000_1200000</t>
+    <t>1990000_50400000</t>
   </si>
   <si>
     <t>档位5</t>
   </si>
   <si>
-    <t>1990000_3000000</t>
+    <t>1990000_126000000</t>
   </si>
   <si>
     <t>排名1</t>
   </si>
   <si>
-    <t>1990000_1500000</t>
+    <t>1990000_157500000</t>
   </si>
   <si>
     <t>排名2</t>
   </si>
   <si>
-    <t>1990000_1000000</t>
+    <t>1990000_120000000</t>
   </si>
   <si>
     <t>排名3</t>
   </si>
   <si>
-    <t>1990000_800000</t>
+    <t>1990000_82500000</t>
   </si>
   <si>
     <t>排名4</t>
   </si>
   <si>
-    <t>1990000_600000</t>
+    <t>1990000_52500000</t>
   </si>
   <si>
     <t>排名5</t>
   </si>
   <si>
-    <t>1990000_400000</t>
+    <t>1990000_30000000</t>
   </si>
   <si>
     <t>排名6-10</t>
@@ -252,7 +252,7 @@
     <t>6_10</t>
   </si>
   <si>
-    <t>1990000_200000</t>
+    <t>1990000_19500000</t>
   </si>
   <si>
     <t>排名11-20</t>
@@ -261,7 +261,7 @@
     <t>11_20</t>
   </si>
   <si>
-    <t>1990000_120000</t>
+    <t>1990000_7500000</t>
   </si>
   <si>
     <t>排名21-50</t>
@@ -270,7 +270,7 @@
     <t>21_50</t>
   </si>
   <si>
-    <t>1990000_100000</t>
+    <t>1990000_4500000</t>
   </si>
 </sst>
 </file>
@@ -453,12 +453,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="10">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="M5" s="2"/>
     </row>
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="10">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="M6" s="2"/>
     </row>
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="10">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="M7" s="2"/>
     </row>
@@ -1519,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="10">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1546,7 +1546,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="10">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
